--- a/client/public/questions.xlsx
+++ b/client/public/questions.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>Title</t>
   </si>
@@ -44,6 +44,18 @@
     <t>Link</t>
   </si>
   <si>
+    <t>Problem Statement</t>
+  </si>
+  <si>
+    <t>Sample Input</t>
+  </si>
+  <si>
+    <t>Sample Output</t>
+  </si>
+  <si>
+    <t>Constraints</t>
+  </si>
+  <si>
     <t>Two Sum</t>
   </si>
   <si>
@@ -56,6 +68,18 @@
     <t>https://leetcode.com/problems/two-sum/</t>
   </si>
   <si>
+    <t>Given an array of integers nums and an integer target, return indices of the two numbers such that they add up to target.</t>
+  </si>
+  <si>
+    <t>nums = [2,7,11,15], target = 9</t>
+  </si>
+  <si>
+    <t>[0,1]</t>
+  </si>
+  <si>
+    <t>2 &lt;= nums.length &lt;= 10^4, -10^9 &lt;= nums[i] &lt;= 10^9</t>
+  </si>
+  <si>
     <t>Longest Substring Without Repeating Chars</t>
   </si>
   <si>
@@ -68,12 +92,36 @@
     <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
   </si>
   <si>
+    <t>Given a string s, find the length of the longest substring without repeating characters.</t>
+  </si>
+  <si>
+    <t>s = 'abcabcbb'</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0 &lt;= s.length &lt;= 5 * 10^4</t>
+  </si>
+  <si>
     <t>Merge Intervals</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/merge-intervals/</t>
   </si>
   <si>
+    <t>Given an array of intervals where intervals[i] = [starti, endi], merge all overlapping intervals.</t>
+  </si>
+  <si>
+    <t>intervals = [[1,3],[2,6],[8,10],[15,18]]</t>
+  </si>
+  <si>
+    <t>[[1,6],[8,10],[15,18]]</t>
+  </si>
+  <si>
+    <t>1 &lt;= intervals.length &lt;= 10^4</t>
+  </si>
+  <si>
     <t>Word Ladder</t>
   </si>
   <si>
@@ -83,25 +131,34 @@
     <t>https://leetcode.com/problems/word-ladder/</t>
   </si>
   <si>
+    <t>Given two words, beginWord and endWord, and a dictionary, return the length of the shortest transformation sequence from beginWord to endWord.</t>
+  </si>
+  <si>
+    <t>beginWord = 'hit', endWord = 'cog', wordList = ['hot','dot','dog','lot','log','cog']</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1 &lt;= beginWord.length &lt;= 10, All words have the same length.</t>
+  </si>
+  <si>
     <t>Binary Tree Level Order Traversal</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/binary-tree-level-order-traversal/</t>
   </si>
   <si>
-    <t>tt</t>
-  </si>
-  <si>
-    <t>yads</t>
-  </si>
-  <si>
-    <t>bnij</t>
-  </si>
-  <si>
-    <t>j</t>
-  </si>
-  <si>
-    <t>g</t>
+    <t>Given the root of a binary tree, return the level order traversal of its nodes' values.</t>
+  </si>
+  <si>
+    <t>root = [3,9,20,null,null,15,7]</t>
+  </si>
+  <si>
+    <t>[[3],[9,20],[15,7]]</t>
+  </si>
+  <si>
+    <t>The number of nodes in the tree is in the range [0, 2000]</t>
   </si>
 </sst>
 </file>
@@ -1097,10 +1154,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <cols>
+    <col min="1" max="1" width="30.203125" customWidth="1"/>
+    <col min="2" max="2" width="25.6484375" customWidth="1"/>
+    <col min="3" max="3" width="20.3046875" customWidth="1"/>
+    <col min="6" max="6" width="26.953125" customWidth="1"/>
+    <col min="7" max="7" width="26.8203125" customWidth="1"/>
+    <col min="8" max="8" width="24.8671875" customWidth="1"/>
+    <col min="9" max="9" width="26.6953125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1116,107 +1182,162 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
+      <c r="E4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
-        <v>10</v>
-      </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/client/public/questions.xlsx
+++ b/client/public/questions.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
   <si>
     <t>Title</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>The number of nodes in the tree is in the range [0, 2000]</t>
+  </si>
+  <si>
+    <t>rans</t>
   </si>
 </sst>
 </file>
@@ -171,7 +174,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,13 +196,6 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -656,149 +652,149 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1154,8 +1150,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="30.203125" customWidth="1"/>
     <col min="2" max="2" width="25.6484375" customWidth="1"/>
@@ -1340,6 +1336,11 @@
         <v>43</v>
       </c>
     </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" display="https://leetcode.com/problems/two-sum/"/>

--- a/client/public/questions.xlsx
+++ b/client/public/questions.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24060" windowHeight="11240"/>
+    <workbookView windowWidth="24060" windowHeight="11080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
+  <si>
+    <t>Topics</t>
+  </si>
   <si>
     <t>Title</t>
   </si>
@@ -56,13 +59,16 @@
     <t>Constraints</t>
   </si>
   <si>
+    <t>Array</t>
+  </si>
+  <si>
     <t>Two Sum</t>
   </si>
   <si>
     <t>Easy</t>
   </si>
   <si>
-    <t>Yes</t>
+    <t>No</t>
   </si>
   <si>
     <t>https://leetcode.com/problems/two-sum/</t>
@@ -86,9 +92,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>https://leetcode.com/problems/longest-substring-without-repeating-characters/</t>
   </si>
   <si>
@@ -143,6 +146,9 @@
     <t>1 &lt;= beginWord.length &lt;= 10, All words have the same length.</t>
   </si>
   <si>
+    <t>Tree</t>
+  </si>
+  <si>
     <t>Binary Tree Level Order Traversal</t>
   </si>
   <si>
@@ -161,7 +167,10 @@
     <t>The number of nodes in the tree is in the range [0, 2000]</t>
   </si>
   <si>
-    <t>rans</t>
+    <t>Graph</t>
+  </si>
+  <si>
+    <t>DFA</t>
   </si>
 </sst>
 </file>
@@ -174,7 +183,14 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,143 +683,144 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1150,93 +1167,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="6"/>
   <cols>
-    <col min="1" max="1" width="30.203125" customWidth="1"/>
-    <col min="2" max="2" width="25.6484375" customWidth="1"/>
-    <col min="3" max="3" width="20.3046875" customWidth="1"/>
-    <col min="6" max="6" width="26.953125" customWidth="1"/>
-    <col min="7" max="7" width="26.8203125" customWidth="1"/>
-    <col min="8" max="8" width="24.8671875" customWidth="1"/>
-    <col min="9" max="9" width="26.6953125" customWidth="1"/>
+    <col min="1" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.3359375" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="26.8359375" customWidth="1"/>
+    <col min="9" max="9" width="24.8359375" customWidth="1"/>
+    <col min="10" max="10" width="26.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
+    <row r="2" spans="1:10">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G3" t="s">
@@ -1248,24 +1271,27 @@
       <c r="I3" t="s">
         <v>24</v>
       </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>25</v>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G4" t="s">
@@ -1277,24 +1303,27 @@
       <c r="I4" t="s">
         <v>30</v>
       </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>31</v>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>34</v>
       </c>
       <c r="G5" t="s">
@@ -1306,48 +1335,67 @@
       <c r="I5" t="s">
         <v>37</v>
       </c>
+      <c r="J5" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>38</v>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
+    <row r="7" spans="1:7">
+      <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="https://leetcode.com/problems/two-sum/"/>
-    <hyperlink ref="E3" r:id="rId2" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/"/>
-    <hyperlink ref="E4" r:id="rId3" display="https://leetcode.com/problems/merge-intervals/"/>
-    <hyperlink ref="E5" r:id="rId4" display="https://leetcode.com/problems/word-ladder/"/>
-    <hyperlink ref="E6" r:id="rId5" display="https://leetcode.com/problems/binary-tree-level-order-traversal/"/>
+    <hyperlink ref="F2" r:id="rId1" display="https://leetcode.com/problems/two-sum/"/>
+    <hyperlink ref="F3" r:id="rId2" display="https://leetcode.com/problems/longest-substring-without-repeating-characters/"/>
+    <hyperlink ref="F4" r:id="rId3" display="https://leetcode.com/problems/merge-intervals/"/>
+    <hyperlink ref="F5" r:id="rId4" display="https://leetcode.com/problems/word-ladder/"/>
+    <hyperlink ref="F6" r:id="rId5" display="https://leetcode.com/problems/binary-tree-level-order-traversal/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
